--- a/data/trans_orig/IP16B03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B03-Estudios-trans_orig.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
